--- a/炼钢北区周边系统清单及通讯方式.xlsx
+++ b/炼钢北区周边系统清单及通讯方式.xlsx
@@ -489,25 +489,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="26.7" customWidth="1" min="3" max="3"/>
-    <col width="19.3" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="32.59999999999999" customWidth="1" min="7" max="7"/>
-    <col width="20.5" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="28.79999999999999" customWidth="1" min="2" max="2"/>
+    <col width="19.3" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="32.59999999999999" customWidth="1" min="6" max="6"/>
+    <col width="12.1" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
     <row r="2" ht="32" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>炼钢北区(二炼钢)周边系统总表 — 2026-09-08 梳理(官方接口整理表20230705+代码证据)</t>
+          <t>炼钢北区(二炼钢)周边系统总表 — 前7列逐字取自官方《外部接口接口整理_20230705》,末列为本次代码梳理印证</t>
         </is>
       </c>
     </row>
@@ -515,1003 +515,929 @@
     <row r="4" ht="28" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>系统名</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>对端系统</t>
+          <t>厂商</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>厂商</t>
+          <t>节点</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>节点</t>
+          <t>现有接口</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>现有接口</t>
+          <t>改造后接口</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>改造后接口</t>
+          <t>电文解析结构</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>电文解析结构/格式</t>
+          <t>备注</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>代码侧印证</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1">
-      <c r="B5" s="3" t="n">
-        <v>1</v>
+          <t>代码侧印证(本次梳理)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>太钢制造管理系统</t>
+        </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>太钢制造管理系统</t>
+          <t>宝信</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>0R</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>框架分发数据增加北区</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>物流运输管理系统</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
           <t>宝信</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>0R</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>JSON(GBK)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>cm_002021 接收制造命令(PSSM);框架分发数据增加北区</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1">
-      <c r="B6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>物流运输管理系统</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>测试:xcom直接通讯
 运行:xcom+IXBUS</t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>JSON(GBK),子母表形式</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>f_xxpa04_snd(铁运车皮,XXPA04)、f_xxsm01_snd(发货码单,7000S4)</t>
-        </is>
-      </c>
+          <t>采用JSON(GBK)，因电文存在子母表形式</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="3" t="n">
-        <v>3</v>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>资源综合利用系统</t>
+        </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>资源综合利用系统</t>
+          <t>宝信</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>铁区动态管控系统</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
           <t>宝信</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>xcom直接通讯</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>mmsm2a_snd/n(给资源铁区发消耗)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1">
-      <c r="B8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>铁区动态管控系统</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>能源动态管控系统</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>宝信\宝能</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>F0</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>前置机+IXBUS</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>xcom+IXBUS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>计量系统</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>宝信自动化</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>EW</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>restful(不走xcom)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>程婕已部署</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>智慧质量系统</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>宝信</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>前置机+IXBUS</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>默认</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>默认格式</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>炼钢二厂南区MES系统（现有系统）</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>中冶赛迪</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>PO</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>xcom+南区前置机</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>TGPO/29S</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>南区接收：北区MES-&gt;前置机-&gt;PO-&gt;南区MES
+南区发送：南区MES-&gt;PO-&gt;前置机-&gt;北区MES</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Broner排程系统</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Broner接收:产销-&gt;PO-&gt;MES(转写Broner需要的本地表)-&gt;Broner读取
+Broner发送:Broner写本地表-&gt;MES读取-&gt;L2</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>不直接通讯</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="n"/>
+    </row>
+    <row r="14" ht="38" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>炼钢一厂不锈钢MES系统</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>山宝</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>U0</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>xcom+一钢前置机</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>TGPO/29S</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>南区接收：北区MES-&gt;前置机-&gt;PO-&gt;南区MES
+南区发送：南区MES-&gt;PO-&gt;前置机-&gt;北区MES</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="38" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>炼钢一厂碳钢MES系统</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>山宝</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>xcom+一钢前置机</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>TGPO/29S</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>南区接收：北区MES-&gt;前置机-&gt;PO-&gt;南区MES
+南区发送：南区MES-&gt;PO-&gt;前置机-&gt;北区MES</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>热连轧2250MES系统</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Psi</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>xcom直接通讯</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>cm_32t809_rcv(铁区库存)、21B004/21B005/21B006 发送</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1">
-      <c r="B9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>能源动态管控系统</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>宝信/宝能</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>F0</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>TGPO/29S</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>北区MES-&gt;2250：框架直接写 2250接口表
+2250-&gt;北区MES：2250写xcom(2250)的sendbuff表</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>热连轧1549MES系统</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>宝信</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>型材厂MES系统</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>宝信</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>不锈线材厂MES系统</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>宝信</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>4300中厚板厂MES系统</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>宝信</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>前置机+IXBUS</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>xcom+IXBUS</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>太钢中板MES</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>宝信</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>前置机+IXBUS</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>xcom直接通讯</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>JSON(GBK)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>TLD协议、JSON(GBK)格式</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>L2 com系统(含板坯库L2系统)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>普瑞特
+中冶南方
+宝信</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>DBLink</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>xcom+独立前置机</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>SHIGANG</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>检化验L2系统前置通讯机</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>EJ</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>DBLink</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>xcom+独立前置机</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>检化验采用oracle，通过ID号为5判断是否给MES</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>炼钢二厂iPlat集控平台</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>宝信自动化</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>数据抽取</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>数据抽取</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>需要协调</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>倒罐站数采系统</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>新建</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>默认</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>倒罐站接收:北区MES-&gt;前置机-&gt;倒罐站读前置机的receviedbuff表
+倒罐站发送：倒罐站-&gt;写前置sentbuff表</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>不锈冷轧系统</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr"/>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>DBLink</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>DBLink</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>10.11.132.212(需要转换成10.162/163/164的)</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>10.13.133.136(现有北区)</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
+    </row>
+    <row r="28" ht="38" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>TPS工艺模型【代码侧补充】</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>宝信</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>cm_nyme01/02_rcv(能源消耗接收)、t8f004/005/007/fsb/se 能源动态发送</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1">
-      <c r="B10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>计量系统</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>宝信自动化</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>EW</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>restful(不走xcom)</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>cm_ewt801_rcv、f_mmsm81_d021_handle_rcv、cm_b02103_rcv;已部署</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1">
-      <c r="B11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>智慧质量系统</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>REST/JSON</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>端点配置在iPlat4C EX04,系统代码MZX_TEST,服务CP_MODEL_TG</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>f_epex_call_rest_tpsmodel*(APBD 3个程序),CRestClient,JSON/UTF-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="38" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>宝武chat消息推送【代码侧补充】</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>宝信</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>前置机+IXBUS</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>默认格式</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>QMTS 工序制造标准 11 工序双向(002113~002123)、cm_200001_rcv</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1">
-      <c r="B12" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>炼钢二厂南区MES</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>中冶赛迪</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>T7</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>xcom+南区前置机</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>TGPO/29S</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>南区接收:北区MES-&gt;前置机-&gt;PO-&gt;南区MES;南区发送反向;北/南标识32处</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1">
-      <c r="B13" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Broner排程系统</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>产销-&gt;PO-&gt;MES(转写Broner本地表)-&gt;Broner读取;发送反向经MES-&gt;L2</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>不直接通讯</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>代码库未见Broner直连(与官方结论一致)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>炼钢一厂不锈钢MES</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>山宝</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>U0</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>xcom+一钢前置机</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>TGPO/29S</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>路由路径同南区MES</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>炼钢一厂碳钢MES</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>山宝</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>V0</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>xcom+一钢前置机</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>TGPO/29S</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="38" customHeight="1">
-      <c r="B16" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>热连轧2250MES</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Psi</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>TGPO/29S</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>北区-&gt;2250:框架直接写2250接口表;2250-&gt;北区:写xcom的sendbuff表</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>热连轧1549MES</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>型材厂MES</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>不锈线材厂MES</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>PO</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>4300中厚板厂MES</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>前置机+IXBUS</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>太钢中板MES</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>前置机+IXBUS</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>xcom直接通讯</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>JSON(GBK),TLD协议</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="B22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>L2 com系统(含板坯库L2)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>普瑞特/中冶南方/宝信</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>DBLink</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>xcom+独立前置机</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>SHIGANG</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>cm_1a1013/15/21转炉实绩收、cm_1a1087连铸切断收、f_mmsm3301板坯原始数据收;发T8E2S1计划状态/PAS1P1出钢计划/PAS1P2铸坯命令/PAS1P3钢种变更/t8e2原料系列</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="38" customHeight="1">
-      <c r="B23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>检化验L2系统前置通讯机</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>EJ</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>DBLink</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>xcom+独立前置机</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>检化验采用Oracle,通过ID号=5判断是否给MES;QMTS检查结果接收(210003)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>炼钢二厂iPlat集控平台</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>宝信自动化</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>数据抽取</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>数据抽取</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>官方表注:需要协调</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="38" customHeight="1">
-      <c r="B25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>倒罐站数采系统</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>ED</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>新建</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>默认</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>北区MES-&gt;前置机receviedbuff;倒罐站-&gt;写前置sentbuff表</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="38" customHeight="1">
-      <c r="B26" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>不锈冷轧系统</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>DBLink</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>DBLink(保留)</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>原10.11.132.212需转换为10.162/163/164(新库网段);现有北区10.13.133.136</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="B27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>TPS工艺模型(代码侧补充)</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>REST/JSON</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>f_epex_call_rest_tpsmodel*(APBD 3个),CRestClient(conn,"MZX_TEST"),服务CP_MODEL_TG,端点在iPlat4C EX04</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="38" customHeight="1">
-      <c r="B28" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>宝武chat消息推送(代码侧补充)</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>宝信</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>EPEX电文</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>EPEX电文</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>含wxurl字段</t>
         </is>
       </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>QMTS f_push_baowu_chat/_dd/_pro、qm_push_baowu_wb,4个程序,消息通知通道</t>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>消息通知通道</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>QMTS f_push_baowu_chat/_dd/_pro、qm_push_baowu_wb(4个程序)</t>
         </is>
       </c>
     </row>
@@ -1535,8 +1461,8 @@
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="10.5" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1593,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="38" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>XCOM 文件传输</t>
@@ -1659,7 +1585,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="38" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>RESTful(HTTP/JSON)</t>
@@ -1703,7 +1629,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>宝武chat推送</t>
@@ -1725,7 +1651,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="70" customHeight="1">
+    <row r="12" ht="54" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>— 未使用通道 —</t>
@@ -2035,8 +1961,8 @@
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2617,7 +2543,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="38" customHeight="1">
+    <row r="25" ht="22" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -2701,7 +2627,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="38" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="B28" s="4" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -2813,7 +2739,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="38" customHeight="1">
+    <row r="32" ht="22" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -3653,7 +3579,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="38" customHeight="1">
+    <row r="62" ht="22" customHeight="1">
       <c r="B62" s="4" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -3677,7 +3603,7 @@
       <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
     </row>
-    <row r="63" ht="38" customHeight="1">
+    <row r="63" ht="22" customHeight="1">
       <c r="B63" s="3" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -3701,7 +3627,7 @@
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr"/>
     </row>
-    <row r="64" ht="38" customHeight="1">
+    <row r="64" ht="22" customHeight="1">
       <c r="B64" s="4" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -3725,7 +3651,7 @@
       <c r="F64" s="4" t="inlineStr"/>
       <c r="G64" s="4" t="inlineStr"/>
     </row>
-    <row r="65" ht="38" customHeight="1">
+    <row r="65" ht="22" customHeight="1">
       <c r="B65" s="3" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -3753,7 +3679,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="38" customHeight="1">
+    <row r="66" ht="22" customHeight="1">
       <c r="B66" s="4" t="inlineStr">
         <is>
           <t>MMSM</t>
@@ -8429,7 +8355,7 @@
       <c r="F241" s="3" t="inlineStr"/>
       <c r="G241" s="3" t="inlineStr"/>
     </row>
-    <row r="242" ht="38" customHeight="1">
+    <row r="242" ht="22" customHeight="1">
       <c r="B242" s="4" t="inlineStr">
         <is>
           <t>PSSM</t>
@@ -8457,7 +8383,7 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="38" customHeight="1">
+    <row r="243" ht="22" customHeight="1">
       <c r="B243" s="3" t="inlineStr">
         <is>
           <t>PSSM</t>
@@ -8485,7 +8411,7 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="38" customHeight="1">
+    <row r="244" ht="22" customHeight="1">
       <c r="B244" s="4" t="inlineStr">
         <is>
           <t>PSSM</t>
@@ -8513,7 +8439,7 @@
         </is>
       </c>
     </row>
-    <row r="245" ht="38" customHeight="1">
+    <row r="245" ht="22" customHeight="1">
       <c r="B245" s="3" t="inlineStr">
         <is>
           <t>PSSM</t>
@@ -8541,7 +8467,7 @@
         </is>
       </c>
     </row>
-    <row r="246" ht="38" customHeight="1">
+    <row r="246" ht="22" customHeight="1">
       <c r="B246" s="4" t="inlineStr">
         <is>
           <t>PSSM</t>
@@ -8569,7 +8495,7 @@
         </is>
       </c>
     </row>
-    <row r="247" ht="38" customHeight="1">
+    <row r="247" ht="22" customHeight="1">
       <c r="B247" s="3" t="inlineStr">
         <is>
           <t>PSSM</t>
@@ -9981,7 +9907,7 @@
         </is>
       </c>
     </row>
-    <row r="299" ht="38" customHeight="1">
+    <row r="299" ht="22" customHeight="1">
       <c r="B299" s="3" t="inlineStr">
         <is>
           <t>QMTS</t>
@@ -10009,7 +9935,7 @@
         </is>
       </c>
     </row>
-    <row r="300" ht="38" customHeight="1">
+    <row r="300" ht="22" customHeight="1">
       <c r="B300" s="4" t="inlineStr">
         <is>
           <t>QMTS</t>
@@ -13850,7 +13776,7 @@
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="11.8" customWidth="1" min="2" max="2"/>
     <col width="35.7" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1"/>
@@ -13896,7 +13822,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="38" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>DM8迁移关系</t>
@@ -13947,7 +13873,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="38" customHeight="1">
       <c r="B9" s="3" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -13981,7 +13907,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="54" customHeight="1">
+    <row r="11" ht="38" customHeight="1">
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -13998,7 +13924,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -14015,7 +13941,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="38" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>说明</t>
